--- a/lit_review_results/1-identification_phase/review_report/first_screening_reviewer_summary.xlsx
+++ b/lit_review_results/1-identification_phase/review_report/first_screening_reviewer_summary.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wolfrieder/PycharmProjects/sok_artifacts/lit_review_results/1-identification_phase/review_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F896510D-3B4F-7F40-9681-651DC905498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7AA7E0-699F-9441-8AD9-6C46400D41F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7320" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$L$704</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6210" uniqueCount="4613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6883" uniqueCount="4613">
   <si>
     <t>Database</t>
   </si>
@@ -13928,35 +13928,23 @@
     <t>Is the paper related to web tracking? A</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Is the paper related to web tracking? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>B</t>
-    </r>
-  </si>
-  <si>
-    <t>final decision</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>Final Decision</t>
+  </si>
+  <si>
+    <t>Is the paper related to web tracking? B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13984,13 +13972,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -14228,7 +14209,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -14322,7 +14303,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -14652,8 +14634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:M705"/>
+  <dimension ref="A1:M704"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -14666,11 +14647,13 @@
     <col min="8" max="8" width="64.33203125" style="26" customWidth="1"/>
     <col min="9" max="9" width="101.6640625" style="23" customWidth="1"/>
     <col min="10" max="10" width="55.83203125" style="21" customWidth="1"/>
-    <col min="11" max="12" width="51.1640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="1"/>
+    <col min="11" max="11" width="56" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="55.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="26" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="25" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -14705,13 +14688,13 @@
         <v>4608</v>
       </c>
       <c r="L1" s="27" t="s">
-        <v>4609</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>4610</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="154" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4612</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>4611</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="154" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -14748,8 +14731,11 @@
       <c r="L2" s="28" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M2" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -14786,8 +14772,11 @@
       <c r="L3" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M3" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -14823,6 +14812,9 @@
       </c>
       <c r="L4" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -14863,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
@@ -14903,8 +14895,11 @@
       <c r="L6" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
@@ -14941,8 +14936,11 @@
       <c r="L7" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -14979,8 +14977,11 @@
       <c r="L8" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -15016,6 +15017,9 @@
       </c>
       <c r="L9" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -15056,10 +15060,10 @@
         <v>0</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -15095,6 +15099,9 @@
       </c>
       <c r="L11" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -15135,7 +15142,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>4611</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="5" customFormat="1" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -15176,10 +15183,10 @@
         <v>0</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>10</v>
       </c>
@@ -15215,6 +15222,9 @@
       </c>
       <c r="L14" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -15255,10 +15265,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>10</v>
       </c>
@@ -15295,8 +15305,11 @@
       <c r="L16" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M16" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>10</v>
       </c>
@@ -15331,8 +15344,11 @@
       <c r="L17" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M17" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>10</v>
       </c>
@@ -15369,8 +15385,11 @@
       <c r="L18" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M18" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>10</v>
       </c>
@@ -15406,6 +15425,9 @@
       </c>
       <c r="L19" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -15446,10 +15468,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>10</v>
       </c>
@@ -15483,6 +15505,9 @@
       </c>
       <c r="L21" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -15523,10 +15548,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>10</v>
       </c>
@@ -15563,8 +15588,11 @@
       <c r="L23" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M23" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>10</v>
       </c>
@@ -15601,8 +15629,11 @@
       <c r="L24" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M24" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>10</v>
       </c>
@@ -15639,8 +15670,11 @@
       <c r="L25" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M25" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>10</v>
       </c>
@@ -15677,8 +15711,11 @@
       <c r="L26" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M26" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>10</v>
       </c>
@@ -15715,8 +15752,11 @@
       <c r="L27" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M27" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>10</v>
       </c>
@@ -15753,8 +15793,11 @@
       <c r="L28" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M28" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>10</v>
       </c>
@@ -15792,10 +15835,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>4611</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>10</v>
       </c>
@@ -15832,8 +15875,11 @@
       <c r="L30" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M30" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>10</v>
       </c>
@@ -15870,8 +15916,11 @@
       <c r="L31" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M31" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>10</v>
       </c>
@@ -15908,8 +15957,11 @@
       <c r="L32" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M32" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>10</v>
       </c>
@@ -15946,8 +15998,11 @@
       <c r="L33" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M33" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>10</v>
       </c>
@@ -15984,8 +16039,11 @@
       <c r="L34" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M34" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>10</v>
       </c>
@@ -16021,6 +16079,9 @@
       </c>
       <c r="L35" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16061,10 +16122,10 @@
         <v>0</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>10</v>
       </c>
@@ -16099,8 +16160,11 @@
       <c r="L37" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M37" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>10</v>
       </c>
@@ -16135,8 +16199,11 @@
       <c r="L38" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M38" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>10</v>
       </c>
@@ -16173,8 +16240,11 @@
       <c r="L39" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M39" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>10</v>
       </c>
@@ -16211,8 +16281,11 @@
       <c r="L40" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M40" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>10</v>
       </c>
@@ -16249,8 +16322,11 @@
       <c r="L41" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M41" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>10</v>
       </c>
@@ -16287,8 +16363,11 @@
       <c r="L42" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M42" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>10</v>
       </c>
@@ -16325,8 +16404,11 @@
       <c r="L43" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M43" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>10</v>
       </c>
@@ -16360,6 +16442,9 @@
       </c>
       <c r="L44" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="45" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16400,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>10</v>
       </c>
@@ -16439,6 +16524,9 @@
       </c>
       <c r="L46" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="47" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16479,10 +16567,10 @@
         <v>0</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>10</v>
       </c>
@@ -16519,8 +16607,11 @@
       <c r="L48" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M48" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>10</v>
       </c>
@@ -16557,8 +16648,11 @@
       <c r="L49" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M49" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>10</v>
       </c>
@@ -16595,8 +16689,11 @@
       <c r="L50" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M50" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>10</v>
       </c>
@@ -16633,8 +16730,11 @@
       <c r="L51" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M51" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>10</v>
       </c>
@@ -16671,8 +16771,11 @@
       <c r="L52" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>10</v>
       </c>
@@ -16709,8 +16812,11 @@
       <c r="L53" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M53" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>10</v>
       </c>
@@ -16747,8 +16853,11 @@
       <c r="L54" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M54" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>10</v>
       </c>
@@ -16784,6 +16893,9 @@
       </c>
       <c r="L55" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -16824,10 +16936,10 @@
         <v>0</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>10</v>
       </c>
@@ -16864,8 +16976,11 @@
       <c r="L57" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M57" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>10</v>
       </c>
@@ -16902,8 +17017,11 @@
       <c r="L58" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M58" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>10</v>
       </c>
@@ -16940,8 +17058,11 @@
       <c r="L59" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M59" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>10</v>
       </c>
@@ -16978,8 +17099,11 @@
       <c r="L60" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M60" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>10</v>
       </c>
@@ -17016,8 +17140,11 @@
       <c r="L61" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M61" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>10</v>
       </c>
@@ -17054,8 +17181,11 @@
       <c r="L62" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M62" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>10</v>
       </c>
@@ -17092,8 +17222,11 @@
       <c r="L63" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M63" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>10</v>
       </c>
@@ -17130,8 +17263,11 @@
       <c r="L64" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M64" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>10</v>
       </c>
@@ -17168,8 +17304,11 @@
       <c r="L65" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M65" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>10</v>
       </c>
@@ -17206,8 +17345,11 @@
       <c r="L66" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M66" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>10</v>
       </c>
@@ -17244,8 +17386,11 @@
       <c r="L67" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M67" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>10</v>
       </c>
@@ -17282,8 +17427,11 @@
       <c r="L68" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M68" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>10</v>
       </c>
@@ -17320,8 +17468,11 @@
       <c r="L69" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M69" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>10</v>
       </c>
@@ -17358,8 +17509,11 @@
       <c r="L70" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M70" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>10</v>
       </c>
@@ -17396,8 +17550,11 @@
       <c r="L71" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M71" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>10</v>
       </c>
@@ -17434,8 +17591,11 @@
       <c r="L72" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M72" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>10</v>
       </c>
@@ -17472,8 +17632,11 @@
       <c r="L73" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M73" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>10</v>
       </c>
@@ -17510,8 +17673,11 @@
       <c r="L74" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M74" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>10</v>
       </c>
@@ -17548,8 +17714,11 @@
       <c r="L75" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" s="5" customFormat="1" ht="325" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M75" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" s="5" customFormat="1" ht="325" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>10</v>
       </c>
@@ -17586,8 +17755,11 @@
       <c r="L76" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M76" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>10</v>
       </c>
@@ -17623,6 +17795,9 @@
       </c>
       <c r="L77" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="78" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -17663,10 +17838,10 @@
         <v>0</v>
       </c>
       <c r="M78" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>10</v>
       </c>
@@ -17703,8 +17878,11 @@
       <c r="L79" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M79" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>10</v>
       </c>
@@ -17741,8 +17919,11 @@
       <c r="L80" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M80" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>10</v>
       </c>
@@ -17779,8 +17960,11 @@
       <c r="L81" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M81" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>10</v>
       </c>
@@ -17815,8 +17999,11 @@
       <c r="L82" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M82" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>10</v>
       </c>
@@ -17853,8 +18040,11 @@
       <c r="L83" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M83" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>10</v>
       </c>
@@ -17891,8 +18081,11 @@
       <c r="L84" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M84" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>10</v>
       </c>
@@ -17929,8 +18122,11 @@
       <c r="L85" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" s="5" customFormat="1" ht="325" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M85" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>10</v>
       </c>
@@ -17967,8 +18163,11 @@
       <c r="L86" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M86" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>10</v>
       </c>
@@ -18003,8 +18202,11 @@
       <c r="L87" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M87" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>10</v>
       </c>
@@ -18041,8 +18243,11 @@
       <c r="L88" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M88" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>10</v>
       </c>
@@ -18078,6 +18283,9 @@
       </c>
       <c r="L89" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -18118,10 +18326,10 @@
         <v>0</v>
       </c>
       <c r="M90" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>10</v>
       </c>
@@ -18158,8 +18366,11 @@
       <c r="L91" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M91" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>10</v>
       </c>
@@ -18195,6 +18406,9 @@
       </c>
       <c r="L92" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M92" s="31" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="93" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -18235,10 +18449,10 @@
         <v>0</v>
       </c>
       <c r="M93" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>10</v>
       </c>
@@ -18275,8 +18489,11 @@
       <c r="L94" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M94" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>10</v>
       </c>
@@ -18312,6 +18529,9 @@
       </c>
       <c r="L95" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M95" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="96" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -18352,10 +18572,10 @@
         <v>0</v>
       </c>
       <c r="M96" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>10</v>
       </c>
@@ -18392,8 +18612,11 @@
       <c r="L97" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M97" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>10</v>
       </c>
@@ -18430,8 +18653,11 @@
       <c r="L98" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M98" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>10</v>
       </c>
@@ -18468,8 +18694,11 @@
       <c r="L99" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M99" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>10</v>
       </c>
@@ -18506,8 +18735,11 @@
       <c r="L100" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M100" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>10</v>
       </c>
@@ -18544,8 +18776,11 @@
       <c r="L101" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M101" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>10</v>
       </c>
@@ -18582,8 +18817,11 @@
       <c r="L102" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M102" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>10</v>
       </c>
@@ -18619,6 +18857,9 @@
       </c>
       <c r="L103" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M103" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="104" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -18659,7 +18900,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="31" t="s">
-        <v>4612</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="105" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -18698,10 +18939,10 @@
         <v>0</v>
       </c>
       <c r="M105" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>10</v>
       </c>
@@ -18737,6 +18978,9 @@
       </c>
       <c r="L106" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M106" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="107" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -18777,10 +19021,10 @@
         <v>0</v>
       </c>
       <c r="M107" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
         <v>10</v>
       </c>
@@ -18816,6 +19060,9 @@
       </c>
       <c r="L108" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M108" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="109" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -18856,10 +19103,10 @@
         <v>0</v>
       </c>
       <c r="M109" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>10</v>
       </c>
@@ -18896,8 +19143,11 @@
       <c r="L110" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M110" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
         <v>11</v>
       </c>
@@ -18934,8 +19184,11 @@
       <c r="L111" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:13" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M111" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>11</v>
       </c>
@@ -18972,8 +19225,11 @@
       <c r="L112" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:13" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M112" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>11</v>
       </c>
@@ -19009,6 +19265,9 @@
       </c>
       <c r="L113" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="114" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -19047,10 +19306,10 @@
         <v>0</v>
       </c>
       <c r="M114" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>11</v>
       </c>
@@ -19087,8 +19346,11 @@
       <c r="L115" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M115" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
         <v>11</v>
       </c>
@@ -19125,8 +19387,11 @@
       <c r="L116" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M116" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>11</v>
       </c>
@@ -19163,8 +19428,11 @@
       <c r="L117" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M117" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>11</v>
       </c>
@@ -19201,8 +19469,11 @@
       <c r="L118" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:13" s="5" customFormat="1" ht="390" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M118" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" s="5" customFormat="1" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
         <v>11</v>
       </c>
@@ -19237,8 +19508,11 @@
       <c r="L119" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:13" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M119" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>11</v>
       </c>
@@ -19275,8 +19549,11 @@
       <c r="L120" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M120" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>11</v>
       </c>
@@ -19313,8 +19590,11 @@
       <c r="L121" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M121" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
         <v>11</v>
       </c>
@@ -19351,8 +19631,11 @@
       <c r="L122" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M122" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>11</v>
       </c>
@@ -19389,8 +19672,11 @@
       <c r="L123" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M123" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>11</v>
       </c>
@@ -19427,8 +19713,11 @@
       <c r="L124" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M124" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>11</v>
       </c>
@@ -19465,8 +19754,11 @@
       <c r="L125" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:13" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M125" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>11</v>
       </c>
@@ -19503,8 +19795,11 @@
       <c r="L126" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:13" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M126" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>11</v>
       </c>
@@ -19541,8 +19836,11 @@
       <c r="L127" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M127" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>11</v>
       </c>
@@ -19577,8 +19875,11 @@
       <c r="L128" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M128" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>11</v>
       </c>
@@ -19615,8 +19916,11 @@
       <c r="L129" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M129" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>11</v>
       </c>
@@ -19653,8 +19957,11 @@
       <c r="L130" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M130" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>11</v>
       </c>
@@ -19690,6 +19997,9 @@
       </c>
       <c r="L131" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="132" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -19730,10 +20040,10 @@
         <v>0</v>
       </c>
       <c r="M132" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
         <v>11</v>
       </c>
@@ -19769,6 +20079,9 @@
       </c>
       <c r="L133" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M133" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="134" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -19807,10 +20120,10 @@
         <v>0</v>
       </c>
       <c r="M134" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
         <v>11</v>
       </c>
@@ -19847,8 +20160,11 @@
       <c r="L135" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:13" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M135" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
         <v>11</v>
       </c>
@@ -19885,8 +20201,11 @@
       <c r="L136" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M136" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>11</v>
       </c>
@@ -19923,8 +20242,11 @@
       <c r="L137" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:13" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M137" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
         <v>11</v>
       </c>
@@ -19961,8 +20283,11 @@
       <c r="L138" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:13" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M138" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>11</v>
       </c>
@@ -19997,8 +20322,11 @@
       <c r="L139" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M139" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>11</v>
       </c>
@@ -20035,8 +20363,11 @@
       <c r="L140" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M140" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>11</v>
       </c>
@@ -20073,8 +20404,11 @@
       <c r="L141" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M141" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
         <v>11</v>
       </c>
@@ -20110,6 +20444,9 @@
       </c>
       <c r="L142" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M142" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="143" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -20150,10 +20487,10 @@
         <v>0</v>
       </c>
       <c r="M143" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>11</v>
       </c>
@@ -20188,8 +20525,11 @@
       <c r="L144" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:13" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M144" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>11</v>
       </c>
@@ -20226,8 +20566,11 @@
       <c r="L145" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M145" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
         <v>11</v>
       </c>
@@ -20264,8 +20607,11 @@
       <c r="L146" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M146" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>11</v>
       </c>
@@ -20301,6 +20647,9 @@
       </c>
       <c r="L147" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M147" s="31" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="148" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -20341,10 +20690,10 @@
         <v>0</v>
       </c>
       <c r="M148" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
         <v>11</v>
       </c>
@@ -20381,8 +20730,11 @@
       <c r="L149" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M149" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
         <v>11</v>
       </c>
@@ -20416,6 +20768,9 @@
       </c>
       <c r="L150" s="29" t="b">
         <v>1</v>
+      </c>
+      <c r="M150" s="2" t="s">
+        <v>4610</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -20454,10 +20809,10 @@
         <v>0</v>
       </c>
       <c r="M151" s="31" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
         <v>11</v>
       </c>
@@ -20493,6 +20848,9 @@
       </c>
       <c r="L152" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M152" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="153" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -20533,10 +20891,10 @@
         <v>0</v>
       </c>
       <c r="M153" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
         <v>11</v>
       </c>
@@ -20573,8 +20931,11 @@
       <c r="L154" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M154" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
         <v>11</v>
       </c>
@@ -20611,8 +20972,11 @@
       <c r="L155" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:13" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M155" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
         <v>11</v>
       </c>
@@ -20649,8 +21013,11 @@
       <c r="L156" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M156" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
         <v>11</v>
       </c>
@@ -20687,8 +21054,11 @@
       <c r="L157" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:13" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M157" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
         <v>11</v>
       </c>
@@ -20725,8 +21095,11 @@
       <c r="L158" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M158" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
         <v>11</v>
       </c>
@@ -20763,8 +21136,11 @@
       <c r="L159" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M159" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
         <v>11</v>
       </c>
@@ -20801,8 +21177,11 @@
       <c r="L160" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M160" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
         <v>11</v>
       </c>
@@ -20839,8 +21218,11 @@
       <c r="L161" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M161" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
         <v>11</v>
       </c>
@@ -20874,6 +21256,9 @@
       </c>
       <c r="L162" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M162" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="163" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -20914,10 +21299,10 @@
         <v>0</v>
       </c>
       <c r="M163" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
         <v>11</v>
       </c>
@@ -20954,8 +21339,11 @@
       <c r="L164" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M164" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
         <v>11</v>
       </c>
@@ -20992,8 +21380,11 @@
       <c r="L165" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M165" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
         <v>11</v>
       </c>
@@ -21030,8 +21421,11 @@
       <c r="L166" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M166" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
         <v>11</v>
       </c>
@@ -21068,8 +21462,11 @@
       <c r="L167" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M167" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
         <v>11</v>
       </c>
@@ -21104,8 +21501,11 @@
       <c r="L168" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="169" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M168" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
         <v>11</v>
       </c>
@@ -21142,8 +21542,11 @@
       <c r="L169" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M169" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
         <v>11</v>
       </c>
@@ -21180,8 +21583,11 @@
       <c r="L170" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M170" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
         <v>11</v>
       </c>
@@ -21216,8 +21622,11 @@
       <c r="L171" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M171" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
         <v>11</v>
       </c>
@@ -21254,8 +21663,11 @@
       <c r="L172" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M172" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
         <v>11</v>
       </c>
@@ -21292,8 +21704,11 @@
       <c r="L173" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M173" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
         <v>11</v>
       </c>
@@ -21328,8 +21743,11 @@
       <c r="L174" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M174" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
         <v>11</v>
       </c>
@@ -21366,8 +21784,11 @@
       <c r="L175" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M175" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
         <v>11</v>
       </c>
@@ -21404,8 +21825,11 @@
       <c r="L176" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:13" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M176" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
         <v>11</v>
       </c>
@@ -21442,8 +21866,11 @@
       <c r="L177" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M177" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
         <v>11</v>
       </c>
@@ -21478,8 +21905,11 @@
       <c r="L178" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M178" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
         <v>11</v>
       </c>
@@ -21516,8 +21946,11 @@
       <c r="L179" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M179" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
         <v>11</v>
       </c>
@@ -21554,8 +21987,11 @@
       <c r="L180" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:13" s="5" customFormat="1" ht="358" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M180" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" s="5" customFormat="1" ht="358" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="s">
         <v>11</v>
       </c>
@@ -21592,8 +22028,11 @@
       <c r="L181" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M181" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
         <v>11</v>
       </c>
@@ -21630,8 +22069,11 @@
       <c r="L182" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:13" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M182" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
         <v>11</v>
       </c>
@@ -21668,8 +22110,11 @@
       <c r="L183" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:13" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M183" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
         <v>11</v>
       </c>
@@ -21706,8 +22151,11 @@
       <c r="L184" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:13" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M184" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
         <v>11</v>
       </c>
@@ -21744,8 +22192,11 @@
       <c r="L185" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M185" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
         <v>11</v>
       </c>
@@ -21780,8 +22231,11 @@
       <c r="L186" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:13" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M186" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="s">
         <v>11</v>
       </c>
@@ -21818,8 +22272,11 @@
       <c r="L187" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:13" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M187" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
         <v>11</v>
       </c>
@@ -21854,8 +22311,11 @@
       <c r="L188" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:13" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M188" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
         <v>11</v>
       </c>
@@ -21892,8 +22352,11 @@
       <c r="L189" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M189" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
         <v>11</v>
       </c>
@@ -21929,6 +22392,9 @@
       </c>
       <c r="L190" s="29" t="b">
         <v>0</v>
+      </c>
+      <c r="M190" s="5" t="s">
+        <v>4609</v>
       </c>
     </row>
     <row r="191" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -21969,10 +22435,10 @@
         <v>0</v>
       </c>
       <c r="M191" s="5" t="s">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
         <v>11</v>
       </c>
@@ -22009,8 +22475,11 @@
       <c r="L192" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M192" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
         <v>11</v>
       </c>
@@ -22047,8 +22516,11 @@
       <c r="L193" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M193" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
         <v>11</v>
       </c>
@@ -22085,8 +22557,11 @@
       <c r="L194" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M194" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
         <v>11</v>
       </c>
@@ -22123,8 +22598,11 @@
       <c r="L195" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M195" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
         <v>11</v>
       </c>
@@ -22159,8 +22637,11 @@
       <c r="L196" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M196" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
         <v>11</v>
       </c>
@@ -22197,8 +22678,11 @@
       <c r="L197" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M197" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
         <v>11</v>
       </c>
@@ -22235,8 +22719,11 @@
       <c r="L198" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M198" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
         <v>11</v>
       </c>
@@ -22271,8 +22758,11 @@
       <c r="L199" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M199" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="s">
         <v>11</v>
       </c>
@@ -22309,8 +22799,11 @@
       <c r="L200" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M200" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
         <v>11</v>
       </c>
@@ -22345,8 +22838,11 @@
       <c r="L201" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:12" s="5" customFormat="1" ht="325" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M201" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
         <v>11</v>
       </c>
@@ -22383,8 +22879,11 @@
       <c r="L202" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M202" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
         <v>11</v>
       </c>
@@ -22421,8 +22920,11 @@
       <c r="L203" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:12" s="5" customFormat="1" ht="70" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M203" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" s="5" customFormat="1" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
         <v>11</v>
       </c>
@@ -22459,8 +22961,11 @@
       <c r="L204" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M204" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
         <v>11</v>
       </c>
@@ -22497,8 +23002,11 @@
       <c r="L205" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M205" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
         <v>11</v>
       </c>
@@ -22533,8 +23041,11 @@
       <c r="L206" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M206" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
         <v>11</v>
       </c>
@@ -22571,8 +23082,11 @@
       <c r="L207" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="208" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M207" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
         <v>11</v>
       </c>
@@ -22609,8 +23123,11 @@
       <c r="L208" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M208" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
         <v>12</v>
       </c>
@@ -22647,8 +23164,11 @@
       <c r="L209" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="210" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M209" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
         <v>12</v>
       </c>
@@ -22685,8 +23205,11 @@
       <c r="L210" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="211" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M210" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A211" s="5" t="s">
         <v>12</v>
       </c>
@@ -22723,8 +23246,11 @@
       <c r="L211" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="212" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M211" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="s">
         <v>12</v>
       </c>
@@ -22761,8 +23287,11 @@
       <c r="L212" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M212" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
         <v>12</v>
       </c>
@@ -22799,8 +23328,11 @@
       <c r="L213" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="214" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M213" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="s">
         <v>12</v>
       </c>
@@ -22837,8 +23369,11 @@
       <c r="L214" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M214" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
         <v>12</v>
       </c>
@@ -22875,8 +23410,11 @@
       <c r="L215" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="216" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M215" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A216" s="5" t="s">
         <v>12</v>
       </c>
@@ -22913,8 +23451,11 @@
       <c r="L216" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M216" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="s">
         <v>12</v>
       </c>
@@ -22951,8 +23492,11 @@
       <c r="L217" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="218" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M217" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
         <v>12</v>
       </c>
@@ -22989,8 +23533,11 @@
       <c r="L218" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M218" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
         <v>12</v>
       </c>
@@ -23027,8 +23574,11 @@
       <c r="L219" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="220" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M219" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
         <v>12</v>
       </c>
@@ -23065,8 +23615,11 @@
       <c r="L220" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="221" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M220" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
         <v>12</v>
       </c>
@@ -23103,8 +23656,11 @@
       <c r="L221" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="222" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M221" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
         <v>12</v>
       </c>
@@ -23141,8 +23697,11 @@
       <c r="L222" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M222" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
         <v>12</v>
       </c>
@@ -23179,8 +23738,11 @@
       <c r="L223" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="224" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M223" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
         <v>12</v>
       </c>
@@ -23217,8 +23779,11 @@
       <c r="L224" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="225" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M224" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
         <v>12</v>
       </c>
@@ -23255,8 +23820,11 @@
       <c r="L225" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:12" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M225" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
         <v>12</v>
       </c>
@@ -23293,8 +23861,11 @@
       <c r="L226" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M226" s="5" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
         <v>12</v>
       </c>
@@ -23331,8 +23902,11 @@
       <c r="L227" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M227" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
         <v>12</v>
       </c>
@@ -23367,8 +23941,11 @@
       <c r="L228" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M228" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
         <v>12</v>
       </c>
@@ -23405,8 +23982,11 @@
       <c r="L229" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="230" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M229" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
         <v>12</v>
       </c>
@@ -23443,8 +24023,11 @@
       <c r="L230" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M230" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
         <v>12</v>
       </c>
@@ -23481,8 +24064,11 @@
       <c r="L231" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="232" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M231" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
         <v>12</v>
       </c>
@@ -23519,8 +24105,11 @@
       <c r="L232" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M232" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
         <v>12</v>
       </c>
@@ -23557,8 +24146,11 @@
       <c r="L233" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:12" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M233" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A234" s="5" t="s">
         <v>12</v>
       </c>
@@ -23595,8 +24187,11 @@
       <c r="L234" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M234" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="s">
         <v>12</v>
       </c>
@@ -23633,8 +24228,11 @@
       <c r="L235" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="236" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M235" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
         <v>12</v>
       </c>
@@ -23671,8 +24269,11 @@
       <c r="L236" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="237" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M236" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
         <v>12</v>
       </c>
@@ -23709,8 +24310,11 @@
       <c r="L237" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M237" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
         <v>12</v>
       </c>
@@ -23747,8 +24351,11 @@
       <c r="L238" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="239" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M238" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A239" s="5" t="s">
         <v>12</v>
       </c>
@@ -23783,8 +24390,11 @@
       <c r="L239" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="240" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M239" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A240" s="5" t="s">
         <v>12</v>
       </c>
@@ -23821,8 +24431,11 @@
       <c r="L240" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="241" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M240" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A241" s="5" t="s">
         <v>12</v>
       </c>
@@ -23857,8 +24470,11 @@
       <c r="L241" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M241" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
         <v>12</v>
       </c>
@@ -23895,8 +24511,11 @@
       <c r="L242" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M242" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
         <v>12</v>
       </c>
@@ -23933,8 +24552,11 @@
       <c r="L243" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M243" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
         <v>12</v>
       </c>
@@ -23971,8 +24593,11 @@
       <c r="L244" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="245" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M244" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
         <v>12</v>
       </c>
@@ -24007,8 +24632,11 @@
       <c r="L245" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="246" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M245" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
         <v>12</v>
       </c>
@@ -24045,8 +24673,11 @@
       <c r="L246" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M246" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
         <v>12</v>
       </c>
@@ -24083,8 +24714,11 @@
       <c r="L247" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="248" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M247" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
         <v>12</v>
       </c>
@@ -24121,8 +24755,11 @@
       <c r="L248" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M248" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
         <v>12</v>
       </c>
@@ -24159,8 +24796,11 @@
       <c r="L249" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M249" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
         <v>12</v>
       </c>
@@ -24197,8 +24837,11 @@
       <c r="L250" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="251" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M250" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
         <v>12</v>
       </c>
@@ -24233,8 +24876,11 @@
       <c r="L251" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="252" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M251" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
         <v>12</v>
       </c>
@@ -24271,8 +24917,11 @@
       <c r="L252" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="253" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M252" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
         <v>12</v>
       </c>
@@ -24309,8 +24958,11 @@
       <c r="L253" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="254" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M253" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
         <v>12</v>
       </c>
@@ -24347,8 +24999,11 @@
       <c r="L254" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="255" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M254" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
         <v>12</v>
       </c>
@@ -24383,8 +25038,11 @@
       <c r="L255" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M255" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
         <v>12</v>
       </c>
@@ -24421,8 +25079,11 @@
       <c r="L256" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="257" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M256" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
         <v>12</v>
       </c>
@@ -24459,8 +25120,11 @@
       <c r="L257" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="258" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M257" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
         <v>12</v>
       </c>
@@ -24497,8 +25161,11 @@
       <c r="L258" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="259" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M258" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
         <v>12</v>
       </c>
@@ -24535,8 +25202,11 @@
       <c r="L259" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="260" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M259" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
         <v>12</v>
       </c>
@@ -24573,8 +25243,11 @@
       <c r="L260" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="261" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M260" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
         <v>12</v>
       </c>
@@ -24611,8 +25284,11 @@
       <c r="L261" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="262" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M261" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="s">
         <v>12</v>
       </c>
@@ -24649,8 +25325,11 @@
       <c r="L262" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="263" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M262" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="s">
         <v>12</v>
       </c>
@@ -24685,8 +25364,11 @@
       <c r="L263" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="264" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M263" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
         <v>12</v>
       </c>
@@ -24721,8 +25403,11 @@
       <c r="L264" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="265" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M264" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
         <v>12</v>
       </c>
@@ -24759,8 +25444,11 @@
       <c r="L265" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="266" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M265" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
         <v>12</v>
       </c>
@@ -24795,8 +25483,11 @@
       <c r="L266" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="267" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M266" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
         <v>12</v>
       </c>
@@ -24833,8 +25524,11 @@
       <c r="L267" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="268" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M267" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A268" s="5" t="s">
         <v>12</v>
       </c>
@@ -24871,8 +25565,11 @@
       <c r="L268" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="269" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M268" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="s">
         <v>12</v>
       </c>
@@ -24907,8 +25604,11 @@
       <c r="L269" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="270" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M269" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="s">
         <v>12</v>
       </c>
@@ -24945,8 +25645,11 @@
       <c r="L270" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="271" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M270" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
         <v>12</v>
       </c>
@@ -24983,8 +25686,11 @@
       <c r="L271" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="272" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M271" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
         <v>12</v>
       </c>
@@ -25019,8 +25725,11 @@
       <c r="L272" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="273" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M272" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
         <v>12</v>
       </c>
@@ -25055,8 +25764,11 @@
       <c r="L273" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M273" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A274" s="5" t="s">
         <v>12</v>
       </c>
@@ -25093,8 +25805,11 @@
       <c r="L274" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="275" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M274" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
         <v>12</v>
       </c>
@@ -25131,8 +25846,11 @@
       <c r="L275" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="276" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M275" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="s">
         <v>12</v>
       </c>
@@ -25169,8 +25887,11 @@
       <c r="L276" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="277" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M276" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A277" s="5" t="s">
         <v>12</v>
       </c>
@@ -25205,8 +25926,11 @@
       <c r="L277" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="278" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M277" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A278" s="5" t="s">
         <v>12</v>
       </c>
@@ -25243,8 +25967,11 @@
       <c r="L278" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M278" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A279" s="5" t="s">
         <v>12</v>
       </c>
@@ -25281,8 +26008,11 @@
       <c r="L279" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="280" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M279" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A280" s="5" t="s">
         <v>12</v>
       </c>
@@ -25319,8 +26049,11 @@
       <c r="L280" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="281" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M280" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="s">
         <v>12</v>
       </c>
@@ -25357,8 +26090,11 @@
       <c r="L281" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="282" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M281" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A282" s="5" t="s">
         <v>12</v>
       </c>
@@ -25395,8 +26131,11 @@
       <c r="L282" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="283" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M282" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="s">
         <v>12</v>
       </c>
@@ -25433,8 +26172,11 @@
       <c r="L283" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="284" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M283" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A284" s="5" t="s">
         <v>12</v>
       </c>
@@ -25469,8 +26211,11 @@
       <c r="L284" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="285" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M284" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
         <v>12</v>
       </c>
@@ -25507,8 +26252,11 @@
       <c r="L285" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="286" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M285" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A286" s="5" t="s">
         <v>12</v>
       </c>
@@ -25545,8 +26293,11 @@
       <c r="L286" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="287" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M286" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="s">
         <v>12</v>
       </c>
@@ -25583,8 +26334,11 @@
       <c r="L287" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M287" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A288" s="5" t="s">
         <v>12</v>
       </c>
@@ -25621,8 +26375,11 @@
       <c r="L288" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="289" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M288" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A289" s="5" t="s">
         <v>12</v>
       </c>
@@ -25657,8 +26414,11 @@
       <c r="L289" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="290" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M289" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A290" s="5" t="s">
         <v>12</v>
       </c>
@@ -25695,8 +26455,11 @@
       <c r="L290" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="291" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M290" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
         <v>12</v>
       </c>
@@ -25731,8 +26494,11 @@
       <c r="L291" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="292" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M291" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A292" s="5" t="s">
         <v>12</v>
       </c>
@@ -25769,8 +26535,11 @@
       <c r="L292" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="293" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M292" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A293" s="5" t="s">
         <v>12</v>
       </c>
@@ -25807,8 +26576,11 @@
       <c r="L293" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="294" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M293" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A294" s="5" t="s">
         <v>12</v>
       </c>
@@ -25845,8 +26617,11 @@
       <c r="L294" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M294" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="s">
         <v>12</v>
       </c>
@@ -25883,8 +26658,11 @@
       <c r="L295" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="296" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M295" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A296" s="5" t="s">
         <v>12</v>
       </c>
@@ -25921,8 +26699,11 @@
       <c r="L296" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="297" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M296" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A297" s="5" t="s">
         <v>12</v>
       </c>
@@ -25959,8 +26740,11 @@
       <c r="L297" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M297" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A298" s="5" t="s">
         <v>12</v>
       </c>
@@ -25997,8 +26781,11 @@
       <c r="L298" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="299" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M298" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A299" s="5" t="s">
         <v>12</v>
       </c>
@@ -26033,8 +26820,11 @@
       <c r="L299" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="300" spans="1:12" s="5" customFormat="1" ht="325" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M299" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" s="5" customFormat="1" ht="325" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A300" s="5" t="s">
         <v>12</v>
       </c>
@@ -26071,8 +26861,11 @@
       <c r="L300" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="301" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M300" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A301" s="5" t="s">
         <v>12</v>
       </c>
@@ -26109,8 +26902,11 @@
       <c r="L301" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="302" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M301" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A302" s="5" t="s">
         <v>12</v>
       </c>
@@ -26147,8 +26943,11 @@
       <c r="L302" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="303" spans="1:12" s="5" customFormat="1" ht="87" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M302" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" s="5" customFormat="1" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A303" s="5" t="s">
         <v>12</v>
       </c>
@@ -26185,8 +26984,11 @@
       <c r="L303" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="304" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M303" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A304" s="5" t="s">
         <v>12</v>
       </c>
@@ -26223,8 +27025,11 @@
       <c r="L304" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="305" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M304" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A305" s="5" t="s">
         <v>12</v>
       </c>
@@ -26261,8 +27066,11 @@
       <c r="L305" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="306" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M305" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A306" s="5" t="s">
         <v>12</v>
       </c>
@@ -26299,8 +27107,11 @@
       <c r="L306" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="307" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M306" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A307" s="5" t="s">
         <v>12</v>
       </c>
@@ -26335,8 +27146,11 @@
       <c r="L307" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="308" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M307" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A308" s="5" t="s">
         <v>12</v>
       </c>
@@ -26373,8 +27187,11 @@
       <c r="L308" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="309" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M308" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A309" s="5" t="s">
         <v>12</v>
       </c>
@@ -26411,8 +27228,11 @@
       <c r="L309" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="310" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M309" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A310" s="5" t="s">
         <v>12</v>
       </c>
@@ -26449,8 +27269,11 @@
       <c r="L310" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="311" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M310" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A311" s="5" t="s">
         <v>12</v>
       </c>
@@ -26487,8 +27310,11 @@
       <c r="L311" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="312" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M311" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A312" s="5" t="s">
         <v>12</v>
       </c>
@@ -26525,8 +27351,11 @@
       <c r="L312" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="313" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M312" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A313" s="5" t="s">
         <v>12</v>
       </c>
@@ -26563,8 +27392,11 @@
       <c r="L313" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="314" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M313" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A314" s="5" t="s">
         <v>12</v>
       </c>
@@ -26597,8 +27429,11 @@
       <c r="L314" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="315" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M314" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A315" s="5" t="s">
         <v>12</v>
       </c>
@@ -26635,8 +27470,11 @@
       <c r="L315" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="316" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M315" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A316" s="5" t="s">
         <v>12</v>
       </c>
@@ -26673,8 +27511,11 @@
       <c r="L316" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="317" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M316" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A317" s="5" t="s">
         <v>12</v>
       </c>
@@ -26711,8 +27552,11 @@
       <c r="L317" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="318" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M317" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A318" s="5" t="s">
         <v>12</v>
       </c>
@@ -26749,8 +27593,11 @@
       <c r="L318" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="319" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M318" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A319" s="5" t="s">
         <v>12</v>
       </c>
@@ -26787,8 +27634,11 @@
       <c r="L319" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="320" spans="1:12" s="5" customFormat="1" ht="87" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M319" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" s="5" customFormat="1" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A320" s="5" t="s">
         <v>12</v>
       </c>
@@ -26825,8 +27675,11 @@
       <c r="L320" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="321" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M320" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A321" s="5" t="s">
         <v>12</v>
       </c>
@@ -26861,8 +27714,11 @@
       <c r="L321" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="322" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M321" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="322" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A322" s="5" t="s">
         <v>12</v>
       </c>
@@ -26899,8 +27755,11 @@
       <c r="L322" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="323" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M322" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A323" s="5" t="s">
         <v>12</v>
       </c>
@@ -26937,8 +27796,11 @@
       <c r="L323" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="324" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M323" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A324" s="5" t="s">
         <v>12</v>
       </c>
@@ -26973,8 +27835,11 @@
       <c r="L324" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="325" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M324" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A325" s="5" t="s">
         <v>12</v>
       </c>
@@ -27011,8 +27876,11 @@
       <c r="L325" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="326" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M325" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A326" s="5" t="s">
         <v>12</v>
       </c>
@@ -27049,8 +27917,11 @@
       <c r="L326" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="327" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M326" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A327" s="5" t="s">
         <v>12</v>
       </c>
@@ -27087,8 +27958,11 @@
       <c r="L327" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="328" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M327" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A328" s="5" t="s">
         <v>12</v>
       </c>
@@ -27125,8 +27999,11 @@
       <c r="L328" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="329" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M328" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A329" s="5" t="s">
         <v>12</v>
       </c>
@@ -27163,8 +28040,11 @@
       <c r="L329" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="330" spans="1:12" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M329" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A330" s="5" t="s">
         <v>12</v>
       </c>
@@ -27201,8 +28081,11 @@
       <c r="L330" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="331" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M330" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A331" s="5" t="s">
         <v>12</v>
       </c>
@@ -27237,8 +28120,11 @@
       <c r="L331" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="332" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M331" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A332" s="5" t="s">
         <v>12</v>
       </c>
@@ -27275,8 +28161,11 @@
       <c r="L332" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="333" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M332" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A333" s="5" t="s">
         <v>12</v>
       </c>
@@ -27311,8 +28200,11 @@
       <c r="L333" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="334" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M333" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A334" s="5" t="s">
         <v>12</v>
       </c>
@@ -27347,8 +28239,11 @@
       <c r="L334" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="335" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M334" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A335" s="5" t="s">
         <v>12</v>
       </c>
@@ -27385,8 +28280,11 @@
       <c r="L335" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="336" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M335" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A336" s="5" t="s">
         <v>12</v>
       </c>
@@ -27423,8 +28321,11 @@
       <c r="L336" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="337" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M336" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A337" s="5" t="s">
         <v>12</v>
       </c>
@@ -27461,8 +28362,11 @@
       <c r="L337" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="338" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M337" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A338" s="5" t="s">
         <v>12</v>
       </c>
@@ -27499,8 +28403,11 @@
       <c r="L338" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="339" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M338" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A339" s="5" t="s">
         <v>12</v>
       </c>
@@ -27537,8 +28444,11 @@
       <c r="L339" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="340" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M339" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A340" s="5" t="s">
         <v>12</v>
       </c>
@@ -27575,8 +28485,11 @@
       <c r="L340" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="341" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M340" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A341" s="5" t="s">
         <v>12</v>
       </c>
@@ -27613,8 +28526,11 @@
       <c r="L341" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="342" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M341" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="s">
         <v>12</v>
       </c>
@@ -27651,8 +28567,11 @@
       <c r="L342" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="343" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M342" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="s">
         <v>12</v>
       </c>
@@ -27689,8 +28608,11 @@
       <c r="L343" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="344" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M343" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A344" s="5" t="s">
         <v>12</v>
       </c>
@@ -27727,8 +28649,11 @@
       <c r="L344" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="345" spans="1:12" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M344" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A345" s="5" t="s">
         <v>12</v>
       </c>
@@ -27765,8 +28690,11 @@
       <c r="L345" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="346" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M345" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="346" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A346" s="5" t="s">
         <v>12</v>
       </c>
@@ -27803,8 +28731,11 @@
       <c r="L346" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="347" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M346" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="347" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A347" s="5" t="s">
         <v>12</v>
       </c>
@@ -27841,8 +28772,11 @@
       <c r="L347" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="348" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M347" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A348" s="5" t="s">
         <v>12</v>
       </c>
@@ -27877,8 +28811,11 @@
       <c r="L348" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="349" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M348" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A349" s="5" t="s">
         <v>12</v>
       </c>
@@ -27915,8 +28852,11 @@
       <c r="L349" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="350" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M349" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A350" s="5" t="s">
         <v>12</v>
       </c>
@@ -27953,8 +28893,11 @@
       <c r="L350" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="351" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M350" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A351" s="5" t="s">
         <v>12</v>
       </c>
@@ -27991,8 +28934,11 @@
       <c r="L351" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="352" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M351" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="352" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A352" s="5" t="s">
         <v>12</v>
       </c>
@@ -28027,8 +28973,11 @@
       <c r="L352" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="353" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M352" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="353" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A353" s="5" t="s">
         <v>12</v>
       </c>
@@ -28065,8 +29014,11 @@
       <c r="L353" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="354" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M353" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A354" s="5" t="s">
         <v>12</v>
       </c>
@@ -28103,8 +29055,11 @@
       <c r="L354" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="355" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M354" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A355" s="5" t="s">
         <v>12</v>
       </c>
@@ -28141,8 +29096,11 @@
       <c r="L355" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="356" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M355" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="356" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A356" s="5" t="s">
         <v>12</v>
       </c>
@@ -28179,8 +29137,11 @@
       <c r="L356" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="357" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M356" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="357" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A357" s="5" t="s">
         <v>12</v>
       </c>
@@ -28217,8 +29178,11 @@
       <c r="L357" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="358" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M357" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="358" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A358" s="5" t="s">
         <v>12</v>
       </c>
@@ -28255,8 +29219,11 @@
       <c r="L358" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="359" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M358" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A359" s="5" t="s">
         <v>12</v>
       </c>
@@ -28291,8 +29258,11 @@
       <c r="L359" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="360" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M359" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="360" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A360" s="5" t="s">
         <v>12</v>
       </c>
@@ -28327,8 +29297,11 @@
       <c r="L360" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="361" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M360" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="361" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A361" s="5" t="s">
         <v>12</v>
       </c>
@@ -28365,8 +29338,11 @@
       <c r="L361" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="362" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M361" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="362" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A362" s="5" t="s">
         <v>12</v>
       </c>
@@ -28403,8 +29379,11 @@
       <c r="L362" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="363" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M362" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A363" s="5" t="s">
         <v>12</v>
       </c>
@@ -28441,8 +29420,11 @@
       <c r="L363" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="364" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M363" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A364" s="5" t="s">
         <v>12</v>
       </c>
@@ -28479,8 +29461,11 @@
       <c r="L364" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="365" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M364" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="365" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A365" s="5" t="s">
         <v>12</v>
       </c>
@@ -28517,8 +29502,11 @@
       <c r="L365" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="366" spans="1:12" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M365" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A366" s="5" t="s">
         <v>12</v>
       </c>
@@ -28555,8 +29543,11 @@
       <c r="L366" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="367" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M366" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="367" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A367" s="5" t="s">
         <v>12</v>
       </c>
@@ -28591,8 +29582,11 @@
       <c r="L367" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="368" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M367" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A368" s="5" t="s">
         <v>12</v>
       </c>
@@ -28629,8 +29623,11 @@
       <c r="L368" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="369" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M368" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A369" s="5" t="s">
         <v>12</v>
       </c>
@@ -28667,8 +29664,11 @@
       <c r="L369" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="370" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M369" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A370" s="5" t="s">
         <v>12</v>
       </c>
@@ -28705,8 +29705,11 @@
       <c r="L370" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="371" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M370" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A371" s="5" t="s">
         <v>12</v>
       </c>
@@ -28743,8 +29746,11 @@
       <c r="L371" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="372" spans="1:12" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M371" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="372" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A372" s="5" t="s">
         <v>12</v>
       </c>
@@ -28781,8 +29787,11 @@
       <c r="L372" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="373" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M372" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A373" s="5" t="s">
         <v>12</v>
       </c>
@@ -28819,8 +29828,11 @@
       <c r="L373" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="374" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M373" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A374" s="5" t="s">
         <v>12</v>
       </c>
@@ -28857,8 +29869,11 @@
       <c r="L374" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="375" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M374" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="375" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A375" s="5" t="s">
         <v>12</v>
       </c>
@@ -28895,8 +29910,11 @@
       <c r="L375" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="376" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M375" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="376" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A376" s="5" t="s">
         <v>12</v>
       </c>
@@ -28933,8 +29951,11 @@
       <c r="L376" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="377" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M376" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="377" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A377" s="5" t="s">
         <v>12</v>
       </c>
@@ -28971,8 +29992,11 @@
       <c r="L377" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="378" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M377" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A378" s="5" t="s">
         <v>12</v>
       </c>
@@ -29009,8 +30033,11 @@
       <c r="L378" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="379" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M378" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A379" s="5" t="s">
         <v>12</v>
       </c>
@@ -29045,8 +30072,11 @@
       <c r="L379" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="380" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M379" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="380" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A380" s="5" t="s">
         <v>12</v>
       </c>
@@ -29083,8 +30113,11 @@
       <c r="L380" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="381" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M380" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="381" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A381" s="5" t="s">
         <v>12</v>
       </c>
@@ -29121,8 +30154,11 @@
       <c r="L381" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="382" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M381" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="382" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A382" s="5" t="s">
         <v>12</v>
       </c>
@@ -29157,8 +30193,11 @@
       <c r="L382" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="383" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M382" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A383" s="5" t="s">
         <v>12</v>
       </c>
@@ -29195,8 +30234,11 @@
       <c r="L383" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="384" spans="1:12" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M383" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="384" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A384" s="5" t="s">
         <v>12</v>
       </c>
@@ -29231,8 +30273,11 @@
       <c r="L384" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="385" spans="1:12" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M384" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A385" s="5" t="s">
         <v>12</v>
       </c>
@@ -29269,8 +30314,11 @@
       <c r="L385" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="386" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M385" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="386" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A386" s="5" t="s">
         <v>12</v>
       </c>
@@ -29305,8 +30353,11 @@
       <c r="L386" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="387" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M386" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A387" s="5" t="s">
         <v>12</v>
       </c>
@@ -29343,8 +30394,11 @@
       <c r="L387" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="388" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M387" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="388" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A388" s="5" t="s">
         <v>12</v>
       </c>
@@ -29381,8 +30435,11 @@
       <c r="L388" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="389" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M388" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A389" s="5" t="s">
         <v>12</v>
       </c>
@@ -29417,8 +30474,11 @@
       <c r="L389" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="390" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M389" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="390" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A390" s="5" t="s">
         <v>12</v>
       </c>
@@ -29453,8 +30513,11 @@
       <c r="L390" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="391" spans="1:12" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M390" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="391" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
         <v>12</v>
       </c>
@@ -29489,8 +30552,11 @@
       <c r="L391" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="392" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M391" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="392" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
         <v>12</v>
       </c>
@@ -29527,8 +30593,11 @@
       <c r="L392" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="393" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M392" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A393" s="5" t="s">
         <v>12</v>
       </c>
@@ -29565,8 +30634,11 @@
       <c r="L393" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="394" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M393" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A394" s="5" t="s">
         <v>12</v>
       </c>
@@ -29603,8 +30675,11 @@
       <c r="L394" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="395" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M394" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="395" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A395" s="5" t="s">
         <v>12</v>
       </c>
@@ -29641,8 +30716,11 @@
       <c r="L395" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="396" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M395" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A396" s="5" t="s">
         <v>12</v>
       </c>
@@ -29677,8 +30755,11 @@
       <c r="L396" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="397" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M396" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="397" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A397" s="5" t="s">
         <v>12</v>
       </c>
@@ -29715,8 +30796,11 @@
       <c r="L397" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="398" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M397" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A398" s="5" t="s">
         <v>12</v>
       </c>
@@ -29753,8 +30837,11 @@
       <c r="L398" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="399" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M398" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="399" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A399" s="5" t="s">
         <v>12</v>
       </c>
@@ -29791,8 +30878,11 @@
       <c r="L399" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="400" spans="1:12" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M399" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A400" s="5" t="s">
         <v>12</v>
       </c>
@@ -29829,8 +30919,11 @@
       <c r="L400" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="401" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M400" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A401" s="5" t="s">
         <v>12</v>
       </c>
@@ -29867,8 +30960,11 @@
       <c r="L401" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="402" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M401" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="402" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A402" s="5" t="s">
         <v>12</v>
       </c>
@@ -29905,8 +31001,11 @@
       <c r="L402" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="403" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M402" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="403" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A403" s="5" t="s">
         <v>12</v>
       </c>
@@ -29943,8 +31042,11 @@
       <c r="L403" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="404" spans="1:12" s="5" customFormat="1" ht="358" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M403" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" s="5" customFormat="1" ht="358" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A404" s="5" t="s">
         <v>12</v>
       </c>
@@ -29981,8 +31083,11 @@
       <c r="L404" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="405" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M404" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="405" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A405" s="5" t="s">
         <v>12</v>
       </c>
@@ -30019,8 +31124,11 @@
       <c r="L405" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="406" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M405" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="406" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A406" s="5" t="s">
         <v>12</v>
       </c>
@@ -30057,8 +31165,11 @@
       <c r="L406" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="407" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M406" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="407" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A407" s="5" t="s">
         <v>12</v>
       </c>
@@ -30095,8 +31206,11 @@
       <c r="L407" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="408" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M407" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A408" s="5" t="s">
         <v>12</v>
       </c>
@@ -30131,8 +31245,11 @@
       <c r="L408" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="409" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M408" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="409" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A409" s="5" t="s">
         <v>12</v>
       </c>
@@ -30169,8 +31286,11 @@
       <c r="L409" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="410" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M409" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="410" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A410" s="5" t="s">
         <v>12</v>
       </c>
@@ -30207,8 +31327,11 @@
       <c r="L410" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="411" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M410" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="411" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A411" s="5" t="s">
         <v>12</v>
       </c>
@@ -30245,8 +31368,11 @@
       <c r="L411" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="412" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M411" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="412" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A412" s="5" t="s">
         <v>12</v>
       </c>
@@ -30283,8 +31409,11 @@
       <c r="L412" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="413" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M412" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="413" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A413" s="5" t="s">
         <v>12</v>
       </c>
@@ -30321,8 +31450,11 @@
       <c r="L413" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="414" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M413" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A414" s="5" t="s">
         <v>12</v>
       </c>
@@ -30359,8 +31491,11 @@
       <c r="L414" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="415" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M414" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A415" s="5" t="s">
         <v>12</v>
       </c>
@@ -30397,8 +31532,11 @@
       <c r="L415" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="416" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M415" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="416" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A416" s="5" t="s">
         <v>12</v>
       </c>
@@ -30435,8 +31573,11 @@
       <c r="L416" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="417" spans="1:12" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M416" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="417" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A417" s="5" t="s">
         <v>12</v>
       </c>
@@ -30473,8 +31614,11 @@
       <c r="L417" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="418" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M417" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="418" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A418" s="5" t="s">
         <v>12</v>
       </c>
@@ -30511,8 +31655,11 @@
       <c r="L418" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="419" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M418" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="419" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A419" s="5" t="s">
         <v>12</v>
       </c>
@@ -30549,8 +31696,11 @@
       <c r="L419" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="420" spans="1:12" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M419" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="420" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A420" s="5" t="s">
         <v>12</v>
       </c>
@@ -30587,8 +31737,11 @@
       <c r="L420" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="421" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M420" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="421" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A421" s="5" t="s">
         <v>12</v>
       </c>
@@ -30625,8 +31778,11 @@
       <c r="L421" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="422" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M421" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="422" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A422" s="5" t="s">
         <v>12</v>
       </c>
@@ -30663,8 +31819,11 @@
       <c r="L422" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="423" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M422" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="423" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A423" s="5" t="s">
         <v>12</v>
       </c>
@@ -30701,8 +31860,11 @@
       <c r="L423" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="424" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M423" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="424" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A424" s="5" t="s">
         <v>12</v>
       </c>
@@ -30739,8 +31901,11 @@
       <c r="L424" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="425" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M424" s="31" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="425" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A425" s="5" t="s">
         <v>12</v>
       </c>
@@ -30775,8 +31940,11 @@
       <c r="L425" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="426" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M425" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="426" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A426" s="5" t="s">
         <v>12</v>
       </c>
@@ -30813,8 +31981,11 @@
       <c r="L426" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="427" spans="1:12" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M426" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="427" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A427" s="5" t="s">
         <v>12</v>
       </c>
@@ -30851,8 +32022,11 @@
       <c r="L427" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="428" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M427" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="428" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A428" s="5" t="s">
         <v>12</v>
       </c>
@@ -30889,8 +32063,11 @@
       <c r="L428" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="429" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M428" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="429" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A429" s="5" t="s">
         <v>12</v>
       </c>
@@ -30927,8 +32104,11 @@
       <c r="L429" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="430" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M429" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="430" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A430" s="5" t="s">
         <v>12</v>
       </c>
@@ -30965,8 +32145,11 @@
       <c r="L430" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="431" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M430" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="431" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A431" s="5" t="s">
         <v>12</v>
       </c>
@@ -31003,8 +32186,11 @@
       <c r="L431" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="432" spans="1:12" s="5" customFormat="1" ht="406" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M431" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="432" spans="1:13" s="5" customFormat="1" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A432" s="5" t="s">
         <v>12</v>
       </c>
@@ -31041,8 +32227,11 @@
       <c r="L432" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="433" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M432" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="433" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A433" s="5" t="s">
         <v>12</v>
       </c>
@@ -31079,8 +32268,11 @@
       <c r="L433" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="434" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M433" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="434" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A434" s="5" t="s">
         <v>12</v>
       </c>
@@ -31117,8 +32309,11 @@
       <c r="L434" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="435" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M434" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="435" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A435" s="5" t="s">
         <v>12</v>
       </c>
@@ -31155,8 +32350,11 @@
       <c r="L435" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="436" spans="1:12" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M435" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="436" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A436" s="5" t="s">
         <v>12</v>
       </c>
@@ -31193,8 +32391,11 @@
       <c r="L436" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="437" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M436" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="437" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A437" s="5" t="s">
         <v>12</v>
       </c>
@@ -31231,8 +32432,11 @@
       <c r="L437" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="438" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M437" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="438" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A438" s="5" t="s">
         <v>12</v>
       </c>
@@ -31269,8 +32473,11 @@
       <c r="L438" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="439" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M438" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="439" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A439" s="5" t="s">
         <v>12</v>
       </c>
@@ -31307,8 +32514,11 @@
       <c r="L439" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="440" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M439" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="440" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A440" s="5" t="s">
         <v>12</v>
       </c>
@@ -31345,8 +32555,11 @@
       <c r="L440" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="441" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M440" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="441" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A441" s="5" t="s">
         <v>12</v>
       </c>
@@ -31383,8 +32596,11 @@
       <c r="L441" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="442" spans="1:12" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M441" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="442" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A442" s="5" t="s">
         <v>12</v>
       </c>
@@ -31419,8 +32635,11 @@
       <c r="L442" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="443" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M442" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="443" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A443" s="5" t="s">
         <v>12</v>
       </c>
@@ -31457,8 +32676,11 @@
       <c r="L443" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="444" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M443" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="444" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A444" s="5" t="s">
         <v>12</v>
       </c>
@@ -31495,8 +32717,11 @@
       <c r="L444" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="445" spans="1:12" s="5" customFormat="1" ht="358" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M444" s="31" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="445" spans="1:13" s="5" customFormat="1" ht="358" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A445" s="5" t="s">
         <v>12</v>
       </c>
@@ -31533,8 +32758,11 @@
       <c r="L445" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="446" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M445" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="446" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A446" s="5" t="s">
         <v>12</v>
       </c>
@@ -31571,8 +32799,11 @@
       <c r="L446" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="447" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M446" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="447" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A447" s="5" t="s">
         <v>12</v>
       </c>
@@ -31609,8 +32840,11 @@
       <c r="L447" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="448" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M447" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="448" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="s">
         <v>12</v>
       </c>
@@ -31645,8 +32879,11 @@
       <c r="L448" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="449" spans="1:12" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M448" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="449" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A449" s="5" t="s">
         <v>12</v>
       </c>
@@ -31681,8 +32918,11 @@
       <c r="L449" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="450" spans="1:12" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M449" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="450" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A450" s="5" t="s">
         <v>12</v>
       </c>
@@ -31717,8 +32957,11 @@
       <c r="L450" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="451" spans="1:12" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M450" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="451" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A451" s="5" t="s">
         <v>12</v>
       </c>
@@ -31755,8 +32998,11 @@
       <c r="L451" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="452" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M451" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="452" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A452" s="5" t="s">
         <v>12</v>
       </c>
@@ -31793,8 +33039,11 @@
       <c r="L452" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="453" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M452" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="453" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A453" s="5" t="s">
         <v>12</v>
       </c>
@@ -31831,8 +33080,11 @@
       <c r="L453" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="454" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M453" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="454" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A454" s="5" t="s">
         <v>12</v>
       </c>
@@ -31869,8 +33121,11 @@
       <c r="L454" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="455" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M454" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="455" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A455" s="5" t="s">
         <v>12</v>
       </c>
@@ -31905,8 +33160,11 @@
       <c r="L455" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="456" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M455" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="456" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A456" s="5" t="s">
         <v>12</v>
       </c>
@@ -31943,8 +33201,11 @@
       <c r="L456" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="457" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M456" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="457" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A457" s="5" t="s">
         <v>12</v>
       </c>
@@ -31981,8 +33242,11 @@
       <c r="L457" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="458" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M457" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="458" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A458" s="5" t="s">
         <v>12</v>
       </c>
@@ -32019,8 +33283,11 @@
       <c r="L458" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="459" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M458" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="459" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A459" s="5" t="s">
         <v>12</v>
       </c>
@@ -32057,8 +33324,11 @@
       <c r="L459" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="460" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M459" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="460" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A460" s="5" t="s">
         <v>12</v>
       </c>
@@ -32095,8 +33365,11 @@
       <c r="L460" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="461" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M460" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="461" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A461" s="5" t="s">
         <v>12</v>
       </c>
@@ -32131,8 +33404,11 @@
       <c r="L461" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="462" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M461" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="462" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A462" s="5" t="s">
         <v>12</v>
       </c>
@@ -32169,8 +33445,11 @@
       <c r="L462" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="463" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M462" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="463" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A463" s="5" t="s">
         <v>12</v>
       </c>
@@ -32207,8 +33486,11 @@
       <c r="L463" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="464" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M463" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="464" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A464" s="5" t="s">
         <v>12</v>
       </c>
@@ -32245,8 +33527,11 @@
       <c r="L464" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="465" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M464" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="465" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="s">
         <v>12</v>
       </c>
@@ -32283,8 +33568,11 @@
       <c r="L465" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="466" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M465" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="466" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A466" s="5" t="s">
         <v>12</v>
       </c>
@@ -32321,8 +33609,11 @@
       <c r="L466" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="467" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M466" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="467" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A467" s="5" t="s">
         <v>12</v>
       </c>
@@ -32359,8 +33650,11 @@
       <c r="L467" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="468" spans="1:12" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M467" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="468" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A468" s="5" t="s">
         <v>12</v>
       </c>
@@ -32397,8 +33691,11 @@
       <c r="L468" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="469" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M468" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="469" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A469" s="5" t="s">
         <v>12</v>
       </c>
@@ -32435,8 +33732,11 @@
       <c r="L469" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="470" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M469" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="470" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A470" s="5" t="s">
         <v>12</v>
       </c>
@@ -32473,8 +33773,11 @@
       <c r="L470" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="471" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M470" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="471" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A471" s="5" t="s">
         <v>12</v>
       </c>
@@ -32511,8 +33814,11 @@
       <c r="L471" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="472" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M471" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="472" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A472" s="5" t="s">
         <v>12</v>
       </c>
@@ -32549,8 +33855,11 @@
       <c r="L472" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="473" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M472" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="473" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A473" s="5" t="s">
         <v>12</v>
       </c>
@@ -32585,8 +33894,11 @@
       <c r="L473" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="474" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M473" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="474" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A474" s="5" t="s">
         <v>12</v>
       </c>
@@ -32621,8 +33933,11 @@
       <c r="L474" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="475" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M474" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="475" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A475" s="5" t="s">
         <v>12</v>
       </c>
@@ -32659,8 +33974,11 @@
       <c r="L475" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="476" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M475" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="476" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A476" s="5" t="s">
         <v>12</v>
       </c>
@@ -32697,8 +34015,11 @@
       <c r="L476" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="477" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M476" s="31" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="477" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A477" s="5" t="s">
         <v>12</v>
       </c>
@@ -32735,8 +34056,11 @@
       <c r="L477" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="478" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M477" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="478" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A478" s="5" t="s">
         <v>12</v>
       </c>
@@ -32773,8 +34097,11 @@
       <c r="L478" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="479" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M478" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="479" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A479" s="5" t="s">
         <v>12</v>
       </c>
@@ -32811,8 +34138,11 @@
       <c r="L479" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="480" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M479" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="480" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A480" s="5" t="s">
         <v>12</v>
       </c>
@@ -32849,8 +34179,11 @@
       <c r="L480" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="481" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M480" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="481" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A481" s="5" t="s">
         <v>12</v>
       </c>
@@ -32887,8 +34220,11 @@
       <c r="L481" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="482" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M481" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="482" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A482" s="5" t="s">
         <v>12</v>
       </c>
@@ -32923,8 +34259,11 @@
       <c r="L482" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="483" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M482" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="483" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A483" s="5" t="s">
         <v>12</v>
       </c>
@@ -32961,8 +34300,11 @@
       <c r="L483" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="484" spans="1:12" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M483" s="5" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="484" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A484" s="5" t="s">
         <v>12</v>
       </c>
@@ -32999,8 +34341,11 @@
       <c r="L484" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="485" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M484" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="485" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A485" s="5" t="s">
         <v>12</v>
       </c>
@@ -33033,8 +34378,11 @@
       <c r="L485" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="486" spans="1:12" s="5" customFormat="1" ht="325" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M485" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="486" spans="1:13" s="5" customFormat="1" ht="325" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A486" s="5" t="s">
         <v>13</v>
       </c>
@@ -33071,8 +34419,11 @@
       <c r="L486" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="487" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M486" s="5" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="487" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
         <v>13</v>
       </c>
@@ -33109,8 +34460,11 @@
       <c r="L487" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="488" spans="1:12" s="5" customFormat="1" ht="87" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M487" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="488" spans="1:13" s="5" customFormat="1" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A488" s="5" t="s">
         <v>13</v>
       </c>
@@ -33145,8 +34499,11 @@
       <c r="L488" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="489" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M488" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="489" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A489" s="5" t="s">
         <v>13</v>
       </c>
@@ -33183,8 +34540,11 @@
       <c r="L489" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="490" spans="1:12" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M489" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="490" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A490" s="5" t="s">
         <v>13</v>
       </c>
@@ -33219,8 +34579,11 @@
       <c r="L490" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="491" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M490" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="491" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A491" s="5" t="s">
         <v>13</v>
       </c>
@@ -33257,8 +34620,11 @@
       <c r="L491" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="492" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M491" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="492" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A492" s="5" t="s">
         <v>13</v>
       </c>
@@ -33295,8 +34661,11 @@
       <c r="L492" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="493" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M492" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="493" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A493" s="5" t="s">
         <v>13</v>
       </c>
@@ -33333,8 +34702,11 @@
       <c r="L493" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="494" spans="1:12" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M493" s="31" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="494" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A494" s="5" t="s">
         <v>13</v>
       </c>
@@ -33371,8 +34743,11 @@
       <c r="L494" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="495" spans="1:12" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M494" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="495" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A495" s="5" t="s">
         <v>13</v>
       </c>
@@ -33409,8 +34784,11 @@
       <c r="L495" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="496" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M495" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="496" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A496" s="5" t="s">
         <v>13</v>
       </c>
@@ -33447,8 +34825,11 @@
       <c r="L496" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="497" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M496" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="497" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A497" s="5" t="s">
         <v>13</v>
       </c>
@@ -33485,8 +34866,11 @@
       <c r="L497" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="498" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M497" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="498" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A498" s="5" t="s">
         <v>13</v>
       </c>
@@ -33523,8 +34907,11 @@
       <c r="L498" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="499" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M498" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="499" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A499" s="5" t="s">
         <v>13</v>
       </c>
@@ -33561,8 +34948,11 @@
       <c r="L499" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="500" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M499" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="500" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A500" s="5" t="s">
         <v>13</v>
       </c>
@@ -33599,8 +34989,11 @@
       <c r="L500" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="501" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M500" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="501" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A501" s="5" t="s">
         <v>13</v>
       </c>
@@ -33637,8 +35030,11 @@
       <c r="L501" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="502" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M501" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="502" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A502" s="5" t="s">
         <v>13</v>
       </c>
@@ -33675,8 +35071,11 @@
       <c r="L502" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="503" spans="1:12" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M502" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="503" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A503" s="5" t="s">
         <v>13</v>
       </c>
@@ -33711,8 +35110,11 @@
       <c r="L503" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="504" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M503" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="504" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A504" s="5" t="s">
         <v>13</v>
       </c>
@@ -33749,8 +35151,11 @@
       <c r="L504" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="505" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M504" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="505" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A505" s="5" t="s">
         <v>13</v>
       </c>
@@ -33787,8 +35192,11 @@
       <c r="L505" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="506" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M505" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="506" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A506" s="5" t="s">
         <v>13</v>
       </c>
@@ -33825,8 +35233,11 @@
       <c r="L506" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="507" spans="1:12" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M506" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="507" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A507" s="5" t="s">
         <v>13</v>
       </c>
@@ -33863,8 +35274,11 @@
       <c r="L507" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="508" spans="1:12" s="5" customFormat="1" ht="409.6" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M507" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="508" spans="1:13" s="5" customFormat="1" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A508" s="5" t="s">
         <v>13</v>
       </c>
@@ -33901,8 +35315,11 @@
       <c r="L508" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="509" spans="1:12" s="5" customFormat="1" ht="358" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M508" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="509" spans="1:13" s="5" customFormat="1" ht="358" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A509" s="5" t="s">
         <v>13</v>
       </c>
@@ -33939,8 +35356,11 @@
       <c r="L509" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="510" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M509" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="510" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A510" s="5" t="s">
         <v>13</v>
       </c>
@@ -33977,8 +35397,11 @@
       <c r="L510" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="511" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M510" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="511" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A511" s="5" t="s">
         <v>13</v>
       </c>
@@ -34011,8 +35434,11 @@
       <c r="L511" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="512" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M511" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="512" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A512" s="5" t="s">
         <v>13</v>
       </c>
@@ -34049,8 +35475,11 @@
       <c r="L512" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="513" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M512" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="513" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A513" s="5" t="s">
         <v>13</v>
       </c>
@@ -34087,8 +35516,11 @@
       <c r="L513" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="514" spans="1:12" s="5" customFormat="1" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M513" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="514" spans="1:13" s="5" customFormat="1" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A514" s="5" t="s">
         <v>13</v>
       </c>
@@ -34125,8 +35557,11 @@
       <c r="L514" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="515" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M514" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="515" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A515" s="5" t="s">
         <v>13</v>
       </c>
@@ -34163,8 +35598,11 @@
       <c r="L515" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="516" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M515" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="516" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A516" s="5" t="s">
         <v>13</v>
       </c>
@@ -34201,8 +35639,11 @@
       <c r="L516" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="517" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M516" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="517" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A517" s="5" t="s">
         <v>13</v>
       </c>
@@ -34239,8 +35680,11 @@
       <c r="L517" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="518" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M517" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="518" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A518" s="5" t="s">
         <v>13</v>
       </c>
@@ -34277,8 +35721,11 @@
       <c r="L518" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="519" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M518" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="519" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A519" s="5" t="s">
         <v>13</v>
       </c>
@@ -34315,8 +35762,11 @@
       <c r="L519" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="520" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M519" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="520" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A520" s="5" t="s">
         <v>13</v>
       </c>
@@ -34353,8 +35803,11 @@
       <c r="L520" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="521" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M520" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="521" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A521" s="5" t="s">
         <v>13</v>
       </c>
@@ -34391,8 +35844,11 @@
       <c r="L521" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="522" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M521" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="522" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A522" s="5" t="s">
         <v>13</v>
       </c>
@@ -34429,8 +35885,11 @@
       <c r="L522" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="523" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M522" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="523" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A523" s="5" t="s">
         <v>13</v>
       </c>
@@ -34465,8 +35924,11 @@
       <c r="L523" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="524" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M523" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="524" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A524" s="5" t="s">
         <v>13</v>
       </c>
@@ -34503,8 +35965,11 @@
       <c r="L524" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="525" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M524" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="525" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A525" s="5" t="s">
         <v>13</v>
       </c>
@@ -34541,8 +36006,11 @@
       <c r="L525" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="526" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M525" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="526" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A526" s="5" t="s">
         <v>13</v>
       </c>
@@ -34579,8 +36047,11 @@
       <c r="L526" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="527" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M526" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="527" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A527" s="5" t="s">
         <v>13</v>
       </c>
@@ -34617,8 +36088,11 @@
       <c r="L527" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="528" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M527" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="528" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A528" s="5" t="s">
         <v>13</v>
       </c>
@@ -34655,8 +36129,11 @@
       <c r="L528" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="529" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M528" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="529" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A529" s="5" t="s">
         <v>13</v>
       </c>
@@ -34693,8 +36170,11 @@
       <c r="L529" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="530" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M529" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="530" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A530" s="5" t="s">
         <v>13</v>
       </c>
@@ -34731,8 +36211,11 @@
       <c r="L530" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="531" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M530" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="531" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A531" s="5" t="s">
         <v>13</v>
       </c>
@@ -34769,8 +36252,11 @@
       <c r="L531" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="532" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M531" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="532" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A532" s="5" t="s">
         <v>13</v>
       </c>
@@ -34807,8 +36293,11 @@
       <c r="L532" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="533" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M532" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="533" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A533" s="5" t="s">
         <v>13</v>
       </c>
@@ -34845,8 +36334,11 @@
       <c r="L533" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="534" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M533" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="534" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A534" s="5" t="s">
         <v>13</v>
       </c>
@@ -34883,8 +36375,11 @@
       <c r="L534" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="535" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M534" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="535" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A535" s="5" t="s">
         <v>13</v>
       </c>
@@ -34921,8 +36416,11 @@
       <c r="L535" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="536" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M535" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="536" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A536" s="5" t="s">
         <v>13</v>
       </c>
@@ -34959,8 +36457,11 @@
       <c r="L536" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="537" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M536" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="537" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A537" s="5" t="s">
         <v>13</v>
       </c>
@@ -34997,8 +36498,11 @@
       <c r="L537" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="538" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M537" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="538" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A538" s="5" t="s">
         <v>13</v>
       </c>
@@ -35035,8 +36539,11 @@
       <c r="L538" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="539" spans="1:12" s="5" customFormat="1" ht="390" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M538" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="539" spans="1:13" s="5" customFormat="1" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A539" s="5" t="s">
         <v>13</v>
       </c>
@@ -35073,8 +36580,11 @@
       <c r="L539" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="540" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M539" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="540" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A540" s="5" t="s">
         <v>13</v>
       </c>
@@ -35111,8 +36621,11 @@
       <c r="L540" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="541" spans="1:12" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M540" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="541" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A541" s="5" t="s">
         <v>13</v>
       </c>
@@ -35149,8 +36662,11 @@
       <c r="L541" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="542" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M541" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="542" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A542" s="5" t="s">
         <v>13</v>
       </c>
@@ -35187,8 +36703,11 @@
       <c r="L542" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="543" spans="1:12" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M542" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="543" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A543" s="5" t="s">
         <v>13</v>
       </c>
@@ -35225,8 +36744,11 @@
       <c r="L543" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="544" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M543" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="544" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A544" s="5" t="s">
         <v>13</v>
       </c>
@@ -35261,8 +36783,11 @@
       <c r="L544" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="545" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M544" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="545" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A545" s="5" t="s">
         <v>13</v>
       </c>
@@ -35299,8 +36824,11 @@
       <c r="L545" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="546" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M545" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="546" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A546" s="5" t="s">
         <v>13</v>
       </c>
@@ -35337,8 +36865,11 @@
       <c r="L546" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="547" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M546" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="547" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A547" s="5" t="s">
         <v>13</v>
       </c>
@@ -35375,8 +36906,11 @@
       <c r="L547" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="548" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M547" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="548" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A548" s="5" t="s">
         <v>13</v>
       </c>
@@ -35411,8 +36945,11 @@
       <c r="L548" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="549" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M548" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="549" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A549" s="5" t="s">
         <v>13</v>
       </c>
@@ -35449,8 +36986,11 @@
       <c r="L549" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="550" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M549" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="550" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A550" s="5" t="s">
         <v>13</v>
       </c>
@@ -35487,8 +37027,11 @@
       <c r="L550" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="551" spans="1:12" s="5" customFormat="1" ht="358" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M550" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="551" spans="1:13" s="5" customFormat="1" ht="358" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A551" s="5" t="s">
         <v>13</v>
       </c>
@@ -35525,8 +37068,11 @@
       <c r="L551" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="552" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M551" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="552" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A552" s="5" t="s">
         <v>13</v>
       </c>
@@ -35563,8 +37109,11 @@
       <c r="L552" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="553" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M552" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A553" s="5" t="s">
         <v>13</v>
       </c>
@@ -35601,8 +37150,11 @@
       <c r="L553" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="554" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M553" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A554" s="5" t="s">
         <v>13</v>
       </c>
@@ -35639,8 +37191,11 @@
       <c r="L554" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="555" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M554" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A555" s="5" t="s">
         <v>13</v>
       </c>
@@ -35677,8 +37232,11 @@
       <c r="L555" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="556" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M555" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A556" s="5" t="s">
         <v>13</v>
       </c>
@@ -35715,8 +37273,11 @@
       <c r="L556" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="557" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M556" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="557" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A557" s="5" t="s">
         <v>13</v>
       </c>
@@ -35749,8 +37310,11 @@
       <c r="L557" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="558" spans="1:12" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M557" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A558" s="5" t="s">
         <v>13</v>
       </c>
@@ -35787,8 +37351,11 @@
       <c r="L558" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="559" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M558" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A559" s="5" t="s">
         <v>13</v>
       </c>
@@ -35825,8 +37392,11 @@
       <c r="L559" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="560" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M559" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A560" s="5" t="s">
         <v>13</v>
       </c>
@@ -35863,8 +37433,11 @@
       <c r="L560" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="561" spans="1:12" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M560" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="561" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A561" s="5" t="s">
         <v>13</v>
       </c>
@@ -35901,8 +37474,11 @@
       <c r="L561" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="562" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M561" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="562" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A562" s="5" t="s">
         <v>13</v>
       </c>
@@ -35939,8 +37515,11 @@
       <c r="L562" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="563" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M562" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A563" s="5" t="s">
         <v>13</v>
       </c>
@@ -35975,8 +37554,11 @@
       <c r="L563" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="564" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M563" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A564" s="5" t="s">
         <v>13</v>
       </c>
@@ -36013,8 +37595,11 @@
       <c r="L564" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="565" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M564" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A565" s="5" t="s">
         <v>13</v>
       </c>
@@ -36051,8 +37636,11 @@
       <c r="L565" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="566" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M565" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A566" s="5" t="s">
         <v>13</v>
       </c>
@@ -36089,8 +37677,11 @@
       <c r="L566" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="567" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M566" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A567" s="5" t="s">
         <v>13</v>
       </c>
@@ -36127,8 +37718,11 @@
       <c r="L567" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="568" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M567" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A568" s="5" t="s">
         <v>13</v>
       </c>
@@ -36165,8 +37759,11 @@
       <c r="L568" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="569" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M568" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A569" s="5" t="s">
         <v>13</v>
       </c>
@@ -36203,8 +37800,11 @@
       <c r="L569" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="570" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M569" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A570" s="5" t="s">
         <v>13</v>
       </c>
@@ -36241,8 +37841,11 @@
       <c r="L570" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="571" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M570" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A571" s="5" t="s">
         <v>13</v>
       </c>
@@ -36279,8 +37882,11 @@
       <c r="L571" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="572" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M571" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="572" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A572" s="5" t="s">
         <v>13</v>
       </c>
@@ -36317,8 +37923,11 @@
       <c r="L572" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="573" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M572" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A573" s="5" t="s">
         <v>13</v>
       </c>
@@ -36355,8 +37964,11 @@
       <c r="L573" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="574" spans="1:12" s="5" customFormat="1" ht="308" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M573" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="574" spans="1:13" s="5" customFormat="1" ht="308" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A574" s="5" t="s">
         <v>13</v>
       </c>
@@ -36393,8 +38005,11 @@
       <c r="L574" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="575" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M574" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="575" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A575" s="5" t="s">
         <v>13</v>
       </c>
@@ -36431,8 +38046,11 @@
       <c r="L575" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="576" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M575" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="576" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A576" s="5" t="s">
         <v>13</v>
       </c>
@@ -36469,8 +38087,11 @@
       <c r="L576" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="577" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M576" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="577" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A577" s="5" t="s">
         <v>13</v>
       </c>
@@ -36507,8 +38128,11 @@
       <c r="L577" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="578" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M577" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="578" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A578" s="5" t="s">
         <v>13</v>
       </c>
@@ -36545,8 +38169,11 @@
       <c r="L578" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="579" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M578" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="579" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A579" s="5" t="s">
         <v>13</v>
       </c>
@@ -36583,8 +38210,11 @@
       <c r="L579" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="580" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M579" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="580" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A580" s="5" t="s">
         <v>13</v>
       </c>
@@ -36621,8 +38251,11 @@
       <c r="L580" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="581" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M580" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="581" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A581" s="5" t="s">
         <v>13</v>
       </c>
@@ -36659,8 +38292,11 @@
       <c r="L581" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="582" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M581" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="582" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A582" s="5" t="s">
         <v>13</v>
       </c>
@@ -36697,8 +38333,11 @@
       <c r="L582" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="583" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M582" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="583" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A583" s="5" t="s">
         <v>13</v>
       </c>
@@ -36735,8 +38374,11 @@
       <c r="L583" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="584" spans="1:12" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M583" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="584" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A584" s="5" t="s">
         <v>13</v>
       </c>
@@ -36773,8 +38415,11 @@
       <c r="L584" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="585" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M584" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="585" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A585" s="5" t="s">
         <v>13</v>
       </c>
@@ -36811,8 +38456,11 @@
       <c r="L585" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="586" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M585" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="586" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A586" s="5" t="s">
         <v>13</v>
       </c>
@@ -36849,8 +38497,11 @@
       <c r="L586" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="587" spans="1:12" s="5" customFormat="1" ht="325" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M586" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="587" spans="1:13" s="5" customFormat="1" ht="325" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A587" s="5" t="s">
         <v>13</v>
       </c>
@@ -36887,8 +38538,11 @@
       <c r="L587" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="588" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M587" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A588" s="5" t="s">
         <v>13</v>
       </c>
@@ -36925,8 +38579,11 @@
       <c r="L588" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="589" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M588" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="589" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A589" s="5" t="s">
         <v>13</v>
       </c>
@@ -36963,8 +38620,11 @@
       <c r="L589" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="590" spans="1:12" s="5" customFormat="1" ht="358" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M589" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13" s="5" customFormat="1" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A590" s="5" t="s">
         <v>13</v>
       </c>
@@ -37001,8 +38661,11 @@
       <c r="L590" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="591" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M590" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="591" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A591" s="5" t="s">
         <v>13</v>
       </c>
@@ -37039,8 +38702,11 @@
       <c r="L591" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="592" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M591" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="592" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A592" s="5" t="s">
         <v>13</v>
       </c>
@@ -37077,8 +38743,11 @@
       <c r="L592" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="593" spans="1:12" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M592" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A593" s="5" t="s">
         <v>13</v>
       </c>
@@ -37115,8 +38784,11 @@
       <c r="L593" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="594" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M593" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A594" s="5" t="s">
         <v>13</v>
       </c>
@@ -37153,8 +38825,11 @@
       <c r="L594" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="595" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M594" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="595" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A595" s="5" t="s">
         <v>13</v>
       </c>
@@ -37191,8 +38866,11 @@
       <c r="L595" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="596" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M595" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="596" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A596" s="5" t="s">
         <v>13</v>
       </c>
@@ -37229,8 +38907,11 @@
       <c r="L596" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="597" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M596" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A597" s="5" t="s">
         <v>13</v>
       </c>
@@ -37267,8 +38948,11 @@
       <c r="L597" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="598" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M597" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A598" s="5" t="s">
         <v>13</v>
       </c>
@@ -37305,8 +38989,11 @@
       <c r="L598" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="599" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M598" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A599" s="5" t="s">
         <v>13</v>
       </c>
@@ -37343,8 +39030,11 @@
       <c r="L599" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="600" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M599" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A600" s="5" t="s">
         <v>13</v>
       </c>
@@ -37379,8 +39069,11 @@
       <c r="L600" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="601" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M600" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A601" s="5" t="s">
         <v>13</v>
       </c>
@@ -37417,8 +39110,11 @@
       <c r="L601" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="602" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M601" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A602" s="5" t="s">
         <v>13</v>
       </c>
@@ -37455,8 +39151,11 @@
       <c r="L602" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="603" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M602" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A603" s="5" t="s">
         <v>13</v>
       </c>
@@ -37493,8 +39192,11 @@
       <c r="L603" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="604" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M603" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="604" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A604" s="5" t="s">
         <v>13</v>
       </c>
@@ -37531,8 +39233,11 @@
       <c r="L604" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="605" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M604" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A605" s="5" t="s">
         <v>13</v>
       </c>
@@ -37569,8 +39274,11 @@
       <c r="L605" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="606" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M605" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A606" s="5" t="s">
         <v>13</v>
       </c>
@@ -37607,8 +39315,11 @@
       <c r="L606" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="607" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M606" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="607" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A607" s="5" t="s">
         <v>13</v>
       </c>
@@ -37643,8 +39354,11 @@
       <c r="L607" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="608" spans="1:12" s="5" customFormat="1" ht="87" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M607" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13" s="5" customFormat="1" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A608" s="5" t="s">
         <v>13</v>
       </c>
@@ -37681,8 +39395,11 @@
       <c r="L608" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="609" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M608" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="609" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A609" s="5" t="s">
         <v>13</v>
       </c>
@@ -37717,8 +39434,11 @@
       <c r="L609" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="610" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M609" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="610" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A610" s="5" t="s">
         <v>13</v>
       </c>
@@ -37755,8 +39475,11 @@
       <c r="L610" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="611" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M610" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="611" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A611" s="5" t="s">
         <v>13</v>
       </c>
@@ -37793,8 +39516,11 @@
       <c r="L611" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="612" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M611" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="612" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A612" s="5" t="s">
         <v>13</v>
       </c>
@@ -37831,8 +39557,11 @@
       <c r="L612" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="613" spans="1:12" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M612" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="613" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A613" s="5" t="s">
         <v>13</v>
       </c>
@@ -37869,8 +39598,11 @@
       <c r="L613" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="614" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M613" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="614" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A614" s="5" t="s">
         <v>13</v>
       </c>
@@ -37905,8 +39637,11 @@
       <c r="L614" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="615" spans="1:12" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M614" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="615" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A615" s="5" t="s">
         <v>13</v>
       </c>
@@ -37943,8 +39678,11 @@
       <c r="L615" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="616" spans="1:12" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M615" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="616" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A616" s="5" t="s">
         <v>13</v>
       </c>
@@ -37981,8 +39719,11 @@
       <c r="L616" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="617" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M616" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="617" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A617" s="5" t="s">
         <v>13</v>
       </c>
@@ -38017,8 +39758,11 @@
       <c r="L617" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="618" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M617" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="618" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A618" s="5" t="s">
         <v>13</v>
       </c>
@@ -38055,8 +39799,11 @@
       <c r="L618" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="619" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M618" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="619" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A619" s="5" t="s">
         <v>13</v>
       </c>
@@ -38091,8 +39838,11 @@
       <c r="L619" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="620" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M619" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="620" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A620" s="5" t="s">
         <v>13</v>
       </c>
@@ -38127,8 +39877,11 @@
       <c r="L620" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="621" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M620" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="621" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A621" s="5" t="s">
         <v>13</v>
       </c>
@@ -38165,8 +39918,11 @@
       <c r="L621" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="622" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M621" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="622" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A622" s="5" t="s">
         <v>13</v>
       </c>
@@ -38201,8 +39957,11 @@
       <c r="L622" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="623" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M622" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="623" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A623" s="5" t="s">
         <v>13</v>
       </c>
@@ -38239,8 +39998,11 @@
       <c r="L623" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="624" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M623" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="624" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A624" s="5" t="s">
         <v>13</v>
       </c>
@@ -38277,8 +40039,11 @@
       <c r="L624" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="625" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M624" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="625" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A625" s="5" t="s">
         <v>13</v>
       </c>
@@ -38315,8 +40080,11 @@
       <c r="L625" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="626" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M625" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="626" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A626" s="5" t="s">
         <v>13</v>
       </c>
@@ -38353,8 +40121,11 @@
       <c r="L626" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="627" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M626" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="627" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A627" s="5" t="s">
         <v>13</v>
       </c>
@@ -38391,8 +40162,11 @@
       <c r="L627" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="628" spans="1:12" s="5" customFormat="1" ht="325" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M627" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="628" spans="1:13" s="5" customFormat="1" ht="325" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A628" s="5" t="s">
         <v>13</v>
       </c>
@@ -38427,8 +40201,11 @@
       <c r="L628" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="629" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M628" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="629" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A629" s="5" t="s">
         <v>13</v>
       </c>
@@ -38461,8 +40238,11 @@
       <c r="L629" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="630" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M629" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="630" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A630" s="5" t="s">
         <v>13</v>
       </c>
@@ -38497,8 +40277,11 @@
       <c r="L630" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="631" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M630" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="631" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A631" s="5" t="s">
         <v>13</v>
       </c>
@@ -38535,8 +40318,11 @@
       <c r="L631" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="632" spans="1:12" s="5" customFormat="1" ht="104" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M631" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="632" spans="1:13" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A632" s="5" t="s">
         <v>13</v>
       </c>
@@ -38571,8 +40357,11 @@
       <c r="L632" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="633" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M632" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="633" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A633" s="5" t="s">
         <v>13</v>
       </c>
@@ -38609,8 +40398,11 @@
       <c r="L633" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="634" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M633" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="634" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A634" s="5" t="s">
         <v>13</v>
       </c>
@@ -38645,8 +40437,11 @@
       <c r="L634" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="635" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M634" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="635" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A635" s="5" t="s">
         <v>13</v>
       </c>
@@ -38681,8 +40476,11 @@
       <c r="L635" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="636" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M635" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="636" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A636" s="5" t="s">
         <v>13</v>
       </c>
@@ -38719,8 +40517,11 @@
       <c r="L636" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="637" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M636" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="637" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A637" s="5" t="s">
         <v>14</v>
       </c>
@@ -38755,8 +40556,11 @@
       <c r="L637" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="638" spans="1:12" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M637" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="638" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A638" s="5" t="s">
         <v>14</v>
       </c>
@@ -38791,8 +40595,11 @@
       <c r="L638" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="639" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M638" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="639" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A639" s="5" t="s">
         <v>14</v>
       </c>
@@ -38827,8 +40634,11 @@
       <c r="L639" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="640" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M639" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="640" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A640" s="5" t="s">
         <v>14</v>
       </c>
@@ -38861,8 +40671,11 @@
       <c r="L640" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="641" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M640" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="641" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A641" s="5" t="s">
         <v>14</v>
       </c>
@@ -38895,8 +40708,11 @@
       <c r="L641" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="642" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M641" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="642" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A642" s="5" t="s">
         <v>14</v>
       </c>
@@ -38929,8 +40745,11 @@
       <c r="L642" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="643" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M642" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="643" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A643" s="5" t="s">
         <v>14</v>
       </c>
@@ -38963,8 +40782,11 @@
       <c r="L643" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="644" spans="1:12" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M643" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="644" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A644" s="5" t="s">
         <v>14</v>
       </c>
@@ -38999,8 +40821,11 @@
       <c r="L644" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="645" spans="1:12" s="5" customFormat="1" ht="325" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M644" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="645" spans="1:13" s="5" customFormat="1" ht="325" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A645" s="5" t="s">
         <v>14</v>
       </c>
@@ -39035,8 +40860,11 @@
       <c r="L645" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="646" spans="1:12" s="5" customFormat="1" ht="358" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M645" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="646" spans="1:13" s="5" customFormat="1" ht="358" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A646" s="5" t="s">
         <v>14</v>
       </c>
@@ -39071,8 +40899,11 @@
       <c r="L646" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="647" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M646" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="647" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A647" s="5" t="s">
         <v>14</v>
       </c>
@@ -39107,8 +40938,11 @@
       <c r="L647" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="648" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M647" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="648" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A648" s="5" t="s">
         <v>14</v>
       </c>
@@ -39143,8 +40977,11 @@
       <c r="L648" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="649" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M648" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="649" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A649" s="5" t="s">
         <v>14</v>
       </c>
@@ -39179,8 +41016,11 @@
       <c r="L649" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="650" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M649" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="650" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A650" s="5" t="s">
         <v>14</v>
       </c>
@@ -39215,8 +41055,11 @@
       <c r="L650" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="651" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M650" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="651" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A651" s="5" t="s">
         <v>15</v>
       </c>
@@ -39253,8 +41096,11 @@
       <c r="L651" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="652" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M651" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="652" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A652" s="5" t="s">
         <v>15</v>
       </c>
@@ -39291,8 +41137,11 @@
       <c r="L652" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="653" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M652" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="653" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A653" s="5" t="s">
         <v>15</v>
       </c>
@@ -39329,8 +41178,11 @@
       <c r="L653" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="654" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M653" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="654" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A654" s="5" t="s">
         <v>15</v>
       </c>
@@ -39367,8 +41219,11 @@
       <c r="L654" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="655" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M654" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="655" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A655" s="5" t="s">
         <v>15</v>
       </c>
@@ -39405,8 +41260,11 @@
       <c r="L655" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="656" spans="1:12" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M655" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="656" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A656" s="5" t="s">
         <v>15</v>
       </c>
@@ -39443,8 +41301,11 @@
       <c r="L656" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="657" spans="1:12" s="5" customFormat="1" ht="87" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M656" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="657" spans="1:13" s="5" customFormat="1" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A657" s="5" t="s">
         <v>15</v>
       </c>
@@ -39481,8 +41342,11 @@
       <c r="L657" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="658" spans="1:12" s="5" customFormat="1" ht="342" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M657" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="658" spans="1:13" s="5" customFormat="1" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A658" s="5" t="s">
         <v>15</v>
       </c>
@@ -39519,8 +41383,11 @@
       <c r="L658" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="659" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M658" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="659" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A659" s="5" t="s">
         <v>15</v>
       </c>
@@ -39557,8 +41424,11 @@
       <c r="L659" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="660" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M659" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="660" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A660" s="5" t="s">
         <v>15</v>
       </c>
@@ -39595,8 +41465,11 @@
       <c r="L660" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="661" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M660" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="661" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A661" s="5" t="s">
         <v>15</v>
       </c>
@@ -39633,8 +41506,11 @@
       <c r="L661" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="662" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M661" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="662" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A662" s="5" t="s">
         <v>15</v>
       </c>
@@ -39671,8 +41547,11 @@
       <c r="L662" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="663" spans="1:12" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M662" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="663" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A663" s="5" t="s">
         <v>15</v>
       </c>
@@ -39709,8 +41588,11 @@
       <c r="L663" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="664" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M663" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="664" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A664" s="5" t="s">
         <v>15</v>
       </c>
@@ -39747,8 +41629,11 @@
       <c r="L664" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="665" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M664" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="665" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A665" s="5" t="s">
         <v>15</v>
       </c>
@@ -39785,8 +41670,11 @@
       <c r="L665" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="666" spans="1:12" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M665" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="666" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A666" s="5" t="s">
         <v>15</v>
       </c>
@@ -39823,8 +41711,11 @@
       <c r="L666" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="667" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M666" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="667" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A667" s="5" t="s">
         <v>15</v>
       </c>
@@ -39861,8 +41752,11 @@
       <c r="L667" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="668" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M667" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="668" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A668" s="5" t="s">
         <v>15</v>
       </c>
@@ -39899,8 +41793,11 @@
       <c r="L668" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="669" spans="1:12" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M668" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="669" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A669" s="5" t="s">
         <v>15</v>
       </c>
@@ -39937,8 +41834,11 @@
       <c r="L669" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="670" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M669" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="670" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A670" s="5" t="s">
         <v>15</v>
       </c>
@@ -39975,8 +41875,11 @@
       <c r="L670" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="671" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M670" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="671" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A671" s="5" t="s">
         <v>15</v>
       </c>
@@ -40013,8 +41916,11 @@
       <c r="L671" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="672" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M671" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="672" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A672" s="5" t="s">
         <v>15</v>
       </c>
@@ -40051,8 +41957,11 @@
       <c r="L672" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="673" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M672" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="673" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A673" s="5" t="s">
         <v>15</v>
       </c>
@@ -40089,8 +41998,11 @@
       <c r="L673" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="674" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M673" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="674" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A674" s="5" t="s">
         <v>15</v>
       </c>
@@ -40127,8 +42039,11 @@
       <c r="L674" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="675" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M674" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="675" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A675" s="5" t="s">
         <v>15</v>
       </c>
@@ -40165,8 +42080,11 @@
       <c r="L675" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="676" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M675" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="676" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A676" s="5" t="s">
         <v>15</v>
       </c>
@@ -40203,8 +42121,11 @@
       <c r="L676" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="677" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M676" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="677" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A677" s="5" t="s">
         <v>15</v>
       </c>
@@ -40241,8 +42162,11 @@
       <c r="L677" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="678" spans="1:12" s="5" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M677" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="678" spans="1:13" s="5" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A678" s="5" t="s">
         <v>15</v>
       </c>
@@ -40279,8 +42203,11 @@
       <c r="L678" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="679" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M678" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="679" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A679" s="5" t="s">
         <v>15</v>
       </c>
@@ -40317,8 +42244,11 @@
       <c r="L679" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="680" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M679" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="680" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A680" s="5" t="s">
         <v>15</v>
       </c>
@@ -40355,8 +42285,11 @@
       <c r="L680" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="681" spans="1:12" s="5" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M680" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="681" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A681" s="5" t="s">
         <v>15</v>
       </c>
@@ -40393,8 +42326,11 @@
       <c r="L681" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="682" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M681" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="682" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A682" s="5" t="s">
         <v>15</v>
       </c>
@@ -40431,8 +42367,11 @@
       <c r="L682" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="683" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M682" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="683" spans="1:13" s="5" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A683" s="5" t="s">
         <v>15</v>
       </c>
@@ -40469,8 +42408,11 @@
       <c r="L683" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="684" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M683" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="684" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A684" s="5" t="s">
         <v>15</v>
       </c>
@@ -40507,8 +42449,11 @@
       <c r="L684" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="685" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M684" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="685" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A685" s="5" t="s">
         <v>15</v>
       </c>
@@ -40545,8 +42490,11 @@
       <c r="L685" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="686" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M685" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="686" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A686" s="5" t="s">
         <v>15</v>
       </c>
@@ -40581,8 +42529,11 @@
       <c r="L686" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="687" spans="1:12" s="5" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M686" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="687" spans="1:13" s="5" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A687" s="5" t="s">
         <v>15</v>
       </c>
@@ -40617,8 +42568,11 @@
       <c r="L687" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="688" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M687" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="688" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A688" s="5" t="s">
         <v>15</v>
       </c>
@@ -40653,8 +42607,11 @@
       <c r="L688" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="689" spans="1:12" s="5" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M688" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="689" spans="1:13" s="5" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A689" s="5" t="s">
         <v>15</v>
       </c>
@@ -40691,8 +42648,11 @@
       <c r="L689" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="690" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M689" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="690" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A690" s="5" t="s">
         <v>15</v>
       </c>
@@ -40729,8 +42689,11 @@
       <c r="L690" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="691" spans="1:12" s="5" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M690" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="691" spans="1:13" s="5" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A691" s="5" t="s">
         <v>15</v>
       </c>
@@ -40767,8 +42730,11 @@
       <c r="L691" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="692" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M691" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="692" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A692" s="5" t="s">
         <v>15</v>
       </c>
@@ -40805,8 +42771,11 @@
       <c r="L692" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="693" spans="1:12" s="5" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M692" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="693" spans="1:13" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A693" s="5" t="s">
         <v>16</v>
       </c>
@@ -40836,8 +42805,11 @@
       <c r="L693" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="694" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M693" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="694" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A694" s="5" t="s">
         <v>16</v>
       </c>
@@ -40869,8 +42841,11 @@
       <c r="L694" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="695" spans="1:12" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M694" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="695" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A695" s="5" t="s">
         <v>16</v>
       </c>
@@ -40904,8 +42879,11 @@
       <c r="L695" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="696" spans="1:12" s="5" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M695" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="696" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A696" s="5" t="s">
         <v>16</v>
       </c>
@@ -40935,8 +42913,11 @@
       <c r="L696" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="697" spans="1:12" s="5" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M696" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="697" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A697" s="5" t="s">
         <v>16</v>
       </c>
@@ -40973,8 +42954,11 @@
       <c r="L697" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="698" spans="1:12" s="5" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M697" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="698" spans="1:13" s="5" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A698" s="5" t="s">
         <v>16</v>
       </c>
@@ -41004,8 +42988,11 @@
       <c r="L698" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="699" spans="1:12" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M698" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="699" spans="1:13" s="5" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A699" s="5" t="s">
         <v>16</v>
       </c>
@@ -41040,8 +43027,11 @@
       <c r="L699" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="700" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M699" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="700" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A700" s="5" t="s">
         <v>16</v>
       </c>
@@ -41071,8 +43061,11 @@
       <c r="L700" s="29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="701" spans="1:12" s="5" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M700" s="2" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="701" spans="1:13" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A701" s="5" t="s">
         <v>16</v>
       </c>
@@ -41102,8 +43095,11 @@
       <c r="L701" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="702" spans="1:12" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M701" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="702" spans="1:13" s="5" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A702" s="5" t="s">
         <v>16</v>
       </c>
@@ -41133,8 +43129,11 @@
       <c r="L702" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="703" spans="1:12" s="5" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="M702" s="31" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="703" spans="1:13" s="5" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A703" s="5" t="s">
         <v>16</v>
       </c>
@@ -41164,26 +43163,17 @@
       <c r="L703" s="29" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="704" spans="1:12" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="M703" s="5" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="704" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="H704" s="24"/>
       <c r="I704" s="25"/>
       <c r="J704" s="22"/>
     </row>
-    <row r="705" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="K1:L704" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="K1:M1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
